--- a/AAII_Financials/Yearly/ALGN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ALGN_YR_FIN.xlsx
@@ -783,10 +783,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1218400</v>
+        <v>1216300</v>
       </c>
       <c r="E9" s="3">
-        <v>1197800</v>
+        <v>1199900</v>
       </c>
       <c r="F9" s="3">
         <v>1155400</v>
@@ -834,10 +834,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2816600</v>
+        <v>2818700</v>
       </c>
       <c r="E10" s="3">
-        <v>2801200</v>
+        <v>2799200</v>
       </c>
       <c r="F10" s="3">
         <v>2706900</v>
@@ -1008,10 +1008,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>127100</v>
+        <v>129100</v>
       </c>
       <c r="E14" s="3">
-        <v>56200</v>
+        <v>54200</v>
       </c>
       <c r="F14" s="3">
         <v>18300</v>
@@ -1128,10 +1128,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3344100</v>
+        <v>3342000</v>
       </c>
       <c r="E17" s="3">
-        <v>3325200</v>
+        <v>3327200</v>
       </c>
       <c r="F17" s="3">
         <v>3205600</v>
@@ -1179,10 +1179,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>690900</v>
+        <v>693000</v>
       </c>
       <c r="E18" s="3">
-        <v>673800</v>
+        <v>671800</v>
       </c>
       <c r="F18" s="3">
         <v>656700</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>856800</v>
+        <v>858800</v>
       </c>
       <c r="E21" s="3">
-        <v>790000</v>
+        <v>787900</v>
       </c>
       <c r="F21" s="3">
         <v>784700</v>
